--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/OHIO_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/OHIO_2020.xlsx
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Montecristo De Guerero</t>
+          <t>Montecristo De Guerrero</t>
         </is>
       </c>
       <c r="C43">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C66">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C105">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C159">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C165">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C214">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C272">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C372">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C409">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C462">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C485">
